--- a/学宫灵灵七（收集表模板）.xlsx
+++ b/学宫灵灵七（收集表模板）.xlsx
@@ -74,7 +74,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,6 +143,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -521,10 +529,11 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>【学宫灵灵七】信息收集表 v2 · 玩法说明</t>
-        </is>
-      </c>
-    </row>
+          <t>【学宫灵灵七】信息收集表 v3 · 玩法说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -533,7 +542,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>学宫灵灵七（代号鸢 25 年学宫主题大富翁，素材包 Act111）</t>
+          <t>学宫灵灵七（代号鸢 25 年学宫主题大富翁活动）</t>
         </is>
       </c>
     </row>
@@ -581,19 +590,19 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>符篆 / 炼器 / 灵药 / 剑道 / 御兽（5 门，素材 Act111_AttIcon_1~8 + up/down）</t>
+          <t>符篆 / 炼器 / 灵药 / 剑道 / 御兽（共 5 门）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>地图点类型(素材确认)</t>
+          <t>地图点类型</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>普通 / 起点(学宫正门) / 学堂(教室) / 考试 / 商店(黄记小卖部) / 社团 / 神庙(许愿) / 自习室 / 办公室 / 传送 / 素材道 / 陷阱 / 男主点 / 打工(兼职) / 巫之学宫(怪物/雪怪)</t>
+          <t>普通 / 起点(学宫正门) / 学堂 / 考试 / 商店(黄记小卖部) / 社团 / 神庙(许愿) / 自习室 / 办公室 / 传送 / 素材道 / 陷阱 / 男主点 / 兼职 / 巫之学宫(怪物/雪怪)</t>
         </is>
       </c>
     </row>
@@ -605,7 +614,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>学堂事件 / 考场(学科问答+突发事) / 自习室(小抄+和男主学习) / 神庙许愿 / 遭遇战PK(怪物) / 恶魔交易 / 命运线(男主剧情) / 社团会馆 / 商店 / 学宫八卦小册 / 兼职 / 新闻文章</t>
+          <t>学堂事件 / 考场(学科问答+突发事) / 自习室(小抄+和男主学习) / 神庙许愿 / 遭遇战PK(怪物) / 恶魔交易 / 命运线(男主剧情) / 社团会馆 / 商店 / 学宫八卦小册 / 兼职</t>
         </is>
       </c>
     </row>
@@ -621,10 +630,11 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>学分等级升级表（数值待实测填写，参照上期'升级村工坊'结构）</t>
+          <t>学分等级升级表（数值待实测填写）</t>
         </is>
       </c>
     </row>
@@ -724,6 +734,7 @@
       <c r="E18" s="6" t="inlineStr"/>
       <c r="F18" s="6" t="inlineStr"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
@@ -734,14 +745,14 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>注2：本模板 sheet 名尽量沿用上期（广陵爱情故事）命名习惯，新增本期独有系统（考场/自习室/神庙/遭遇战/恶魔交易/命运线）；</t>
+          <t>注2：黄色高亮行 = 已按游戏录屏填写完成的样例（考场·学科问答题库），其余 sheet 待填充；</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>注3：素材包 G:\代号鸢wiki\导出\260819\新建文件夹\007-1(124图) / 007-2(1050图, Act111_*) 为游戏UI导出，页面部署时按需引用。</t>
+          <t>注3：本表不使用游戏文件内资源，配图请用游戏内截图存档。</t>
         </is>
       </c>
     </row>
@@ -768,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -836,14 +847,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>本期新系统（素材：Act111_Entry_emojiaoyi_* 恶魔交易入口/全屏背景、light 高亮、numberbg 数值框）；机制待实测（可能是用属性/货币交换随机收益）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>另：早恋提示（Act111_Entry_zaolian_*）与素材道（sucaidao）等特殊入口，如遇文本同样记录。</t>
+          <t>本期新系统（恶魔交易/早恋等特殊入口）；机制待实测（可能是用属性/货币交换随机收益）。</t>
         </is>
       </c>
     </row>
@@ -925,7 +929,7 @@
       <c r="E2" s="10" t="inlineStr"/>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>截图：168_009</t>
+          <t>视频168 约09分</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1366,7 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>截图：170_015</t>
+          <t>视频170 约15分</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1393,7 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>截图：169_010</t>
+          <t>视频169 约10分</t>
         </is>
       </c>
     </row>
@@ -1419,17 +1423,17 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>老师</t>
+          <t>学堂</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>（狮子庙/文丑/徐庶/张绣/张仲景）</t>
+          <t>（张角/张仲景/贾诩等老师）</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>（教师 NPC 台词，素材 Act111_Entry_Teacher_*）</t>
+          <t>（教师 NPC 台词）</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -1442,7 +1446,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>对应上期'船夫 村集 博戏坊对话'；教师头像素材：Act111_Entry_Teacher_shizimiao/wenchou/xushu/zhangxiu/zhangzhongjing、Act111_Pixel_*（像素头像）。</t>
+          <t>对应上期'船夫 村集 博戏坊对话'；固定台词与剧情对白分开记录。</t>
         </is>
       </c>
     </row>
@@ -1457,13 +1461,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1482,11 +1485,6 @@
           <t>类型</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>素材对应</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
@@ -1504,11 +1502,6 @@
           <t>起点</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>Act111_MapPoint_qidian / House_qidian</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -1526,11 +1519,6 @@
           <t>事件格</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_jiaoshi / House_jiaoshi</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -1548,11 +1536,6 @@
           <t>考试格</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_kaoshi / House_kaoshi</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -1570,11 +1553,6 @@
           <t>商店</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_shangdian / House_shangdian</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -1592,11 +1570,6 @@
           <t>专项格</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_shetuan / House_shetuan</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -1606,17 +1579,12 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>（许愿地点，对应 God 许愿系统）</t>
+          <t>（许愿地点，对应许愿系统）</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>许愿格</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_shenmiao / House_shenmiao</t>
         </is>
       </c>
     </row>
@@ -1636,11 +1604,6 @@
           <t>学习格</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_zixi / House_zixi</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -1658,11 +1621,6 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_bangongshi / House_bangongshi</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1680,11 +1638,6 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_chuansong / House_chuansong</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1702,11 +1655,6 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_sucaidao / sucai</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -1716,17 +1664,12 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>（陷阱格 xianji）</t>
+          <t>（陷阱格）</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
           <t>危险格</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_xianji_wu</t>
         </is>
       </c>
     </row>
@@ -1746,16 +1689,11 @@
           <t>邂逅格</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_nanzhu / House_*五男主</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>打工/兼职</t>
+          <t>兼职</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -1766,11 +1704,6 @@
       <c r="C14" s="10" t="inlineStr">
         <is>
           <t>兼职格</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_dagong_wu / Entry_Work</t>
         </is>
       </c>
     </row>
@@ -1790,11 +1723,6 @@
           <t>特殊格</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Main_xueguai_tips / Monster_img*</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -1812,16 +1740,11 @@
           <t>普通格</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>MapPoint_putong / daolu</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>素材命名揭示的完整地点体系（MapPoint/House/MapInfo_icon 三套图标对应同一地点）；可在游戏内'地点信息'面板逐格核对补充。</t>
+          <t>可在游戏内'地点信息'面板逐格点开核对补充。</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1865,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>对应上期'发展目标'；任务素材：Act111_TaskItem_*、Act111_TaskProgress_*。</t>
+          <t>对应上期'发展目标'。</t>
         </is>
       </c>
     </row>
@@ -2017,7 +1940,7 @@
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>截图：168_004</t>
+          <t>视频168 约04分</t>
         </is>
       </c>
     </row>
@@ -2120,14 +2043,14 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>截图：168_005</t>
+          <t>视频168 约05分</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>对应上期'小卖部'（活动商店）；心纸裳校服图标：007-1 icon_cloth_furong/liubian/sunce/yuanji/zuoci。</t>
+          <t>对应上期'小卖部'（活动商店）；兑换界面文本（'请选择需要兑换的道具/拥有0/确认兑换'）一并记录。</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2123,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>对应上期'村工坊 事件记录'（截图存档）；学堂事件/考试/突发事/许愿/遭遇战等均可在此按行粘贴截图留档。</t>
+          <t>学堂事件/考试/突发事/许愿/遭遇战等均可在此按行粘贴游戏内截图留档。</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2410,14 +2333,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>结构同上一期：==引导剧情== / ==学宫·一~N== / 各男主剧情线壹贰叁终；每段头尾放 {{对话-头}} / {{对话-尾}}；</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>素材参考：Act111_FateLine_*（命运线卡片 fr/lb/sc/yj/zc=傅融/刘辩/孙策/袁基/左慈）、Act111_Entry_PlotItem_*（剧情条目图标）。</t>
+          <t>结构同上一期：==引导剧情== / ==学宫·一~N== / 各男主剧情线壹贰叁终；每段头尾放 {{对话-头}} / {{对话-尾}}。</t>
         </is>
       </c>
     </row>
@@ -2550,14 +2466,14 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>对应上期'5男主地点邂逅' + 本期'命运线'（Act111_FateLine_*）；每男主按 壹/贰/叁/终 分段；</t>
+          <t>对应上期'5男主地点邂逅' + 本期'命运线'；每男主按 壹/贰/叁/终 分段；</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>记录结识/同行中状态、同行小插曲、以及男主对应地点（素材：Act111_House_yuanji 等五男主房屋、Act111_Map_head_* 地图头像）。</t>
+          <t>记录结识/同行中状态、同行小插曲、男主对应地点（袁基：学生会会长·炼器屋）。</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2652,7 +2568,7 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>截图：168_013</t>
+          <t>视频168 约13分</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2603,7 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>截图：170_010</t>
+          <t>视频170 约10分</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2638,7 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>截图：170_020</t>
+          <t>视频170 约20分</t>
         </is>
       </c>
     </row>
@@ -2752,14 +2668,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>对应上期'事件卡（已转至村工坊）'；素材：Act111_Entry_jiaoshi_*（学堂抽取 jz1~6 事件格、God1/God2 buff、chou=抽取）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>风水观 buff 图标：007-1 icon_buff_dfw2_*。</t>
+          <t>对应上期'事件卡（已转至村工坊）'；事件抽取界面有 6 个事件格与 buff 格，逐格记录。</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2836,139 +2745,156 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n">
+      <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>符篆</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>绘制高阶符篆对修士的核心要求是？</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>必须闭眼绘制</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>至少连续通宵三天不睡</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>灵力储备充足且精纯</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>灵力储备充足且精纯</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr"/>
-      <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>截图：168_032</t>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>考试进度 0</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>视频168 约32分</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="n">
+      <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>灵药</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>以下哪种灵草在完全无光的环境中也能生长？</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>所有绿色植物都需要光照进行光合作用</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>仙人掌可以在黑暗中生长</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>蘑菇可以在黑暗中生长</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>蘑菇可以在黑暗中生长</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr"/>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>截图：168_045</t>
+      <c r="H3" s="11" t="inlineStr"/>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>视频168 约45分</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="n">
+      <c r="A4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>御兽</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>御兽师给灵兽下达指令时，最重要的原则是？</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>用完整的句子跟它解释为什么</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>说话声音越大越有效</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>指令简短一致，每次用相同的词语和手势</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>指令简短一致，每次用相同的词语和手势</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr"/>
-      <c r="I4" s="10" t="inlineStr">
-        <is>
-          <t>截图：170_002</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>考场=上期'工作站 遭遇战'对应系统；素材：Act111_Entry_kaochang_*（考场界面）、Act111_kaochang_*（进度条/图标）、AttIcon_1~8（学科图标）；</t>
-        </is>
-      </c>
+      <c r="H4" s="11" t="inlineStr"/>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>视频170 约02分</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr"/>
+      <c r="C5" s="10" t="inlineStr"/>
+      <c r="D5" s="10" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>学科图标对应：符篆/炼器/灵药/剑道/御兽 的 up/down 图标（Act111_AttIcon_up*/down*），收录时标注。</t>
+          <t>考场=上期'工作站 遭遇战'对应系统；考试时弹出【学科问答】选择题，逐题收集（题目+3选项+正确答案）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>黄色高亮行为已填写样例（来源：游戏录屏OCR）；答案不明确时先标注'待确认'。</t>
         </is>
       </c>
     </row>
@@ -3063,7 +2989,7 @@
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>截图：168_011</t>
+          <t>视频168 约11分</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3076,7 @@
       <c r="E2" s="10" t="inlineStr"/>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>截图：169_003</t>
+          <t>视频169 约03分</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3149,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>本期新系统（上期无对应）；素材：Act111_zixishi_*（自习室：readycheat=准备小抄/studyalone=独自学习/studychat=一起学习/study_fr/lb/sc/yj/zc=和五男主学习）、Act111_Entry_zixishi_*。</t>
+          <t>本期新系统（上期无对应）；自习室可独自学习、与男主一起学习、准备小抄。</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3321,14 +3247,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>对应上期'王母庙 筊杯问神'；素材：Act111_Entry_God_*（神像头像 gj=郭嘉/kr=孔融/ls=?/mc=马超/szm=狮子庙/wc=文丑/xs=徐庶/zgl=张角/zx=左慈?/zzj=张仲景）、Act111_God_1~8、Act111_godbuff_*；</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>许愿结果分好/坏（God_badbg/God_goodbg），逐条记录。</t>
+          <t>对应上期'王母庙 筊杯问神'；许愿结果分好/坏，逐条记录。</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3403,7 +3322,7 @@
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>（怪物形象：Act111_Monster_img* / xueguai）</t>
+          <t>（怪物形象待截图）</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
@@ -3426,14 +3345,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>对应上期'工作站 遭遇战v2.0'；素材：Act111_Enemy_*（敌人 baoli 暴力/money 金钱/PkNum/resulttxt）、Act111_GameView_pk*（PK界面）、Act111_Monster_img*、pf_xs_xueguai*；</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>巫之学宫/雪怪区域：前进不消耗通行骰子，怪物持续移动，需拉开距离（素材 Act111_Main_xueguai_tips）。</t>
+          <t>对应上期'工作站 遭遇战v2.0'；巫之学宫/雪怪区域：前进不消耗通行骰子，怪物持续移动，需拉开距离。</t>
         </is>
       </c>
     </row>

--- a/学宫灵灵七（收集表模板）.xlsx
+++ b/学宫灵灵七（收集表模板）.xlsx
@@ -533,7 +533,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -630,7 +629,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -734,7 +732,6 @@
       <c r="E18" s="6" t="inlineStr"/>
       <c r="F18" s="6" t="inlineStr"/>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
@@ -2538,137 +2535,172 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n">
+      <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>学堂</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>事件卡·风水观</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>淘到绝版《符篆入门》</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>在学宫跳蚤市场淘到一本绝版《符篆入门》，示例图来自张角老师亲笔，裁下来竟能直接使用。</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>符篆+20（风水观：学堂能力成长时效果提升400%，剩余1次）</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>视频168 约13分</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>学堂</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>事件卡</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>淘到绝版《符篆入门》</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>在学宫跳蚤市场淘到一本绝版《符篆入门》，示例图来自张角老师亲笔，裁下来竟能直接使用。</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>符篆+20（风水观：学堂能力成长时效果提升400%，剩余1次）</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>视频168 约13分</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>煮糊药茶</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>按张仲景学长提供的方子烹煮药茶，但因灶火太猛直接煮糊了，意外发现焦糊的茶渣驱蚊效果一流。</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>灵药+4</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>视频170 约10分</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>学堂</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>事件卡</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>煮糊药茶</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>按张仲景学长提供的方子烹煮药茶，但因灶火太猛直接煮糊了，意外发现焦糊的茶渣驱蚊效果一流。</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>灵药+4</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>视频170 约10分</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>拐杖制敌</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>贾诩学长表示一把拐杖也能制敌，关键是把手想象成最讨厌的人。看着木人桩上贴着的郭嘉画像，同学们陷入沉默。</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>剑道+4</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>视频170 约20分</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>学堂</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>事件卡</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>拐杖制敌</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>贾诩学长表示一把拐杖也能制敌，关键是把手想象成最讨厌的人。看着木人桩上贴着的郭嘉画像，同学们陷入沉默。</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>剑道+4</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>视频170 约20分</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>怀疑飞云被霸凌</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>（事件内容待补录：仅截到事件名称）</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>（结果待补录）</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>视频170 约21分</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>学堂</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>事件卡</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>（随机事件文本：学科+2/+4/+20(风水观)/全学科+1）</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr"/>
-      <c r="G5" s="10" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>（随机事件文本：学科+2 / +4 / +20(风水观) / 全学科+1）</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>对应上期'事件卡（已转至村工坊）'；事件抽取界面有 6 个事件格与 buff 格，逐格记录。</t>
+          <t>对应上期「事件卡（已转至村工坊）」；事件抽取界面有 6 个事件格与 buff 格；黄色高亮=已按视频OCR填写（3条完整+1条待补），其余待收集。</t>
         </is>
       </c>
     </row>

--- a/学宫灵灵七（收集表模板）.xlsx
+++ b/学宫灵灵七（收集表模板）.xlsx
@@ -15,15 +15,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="考场 突发事与选项" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自习室·小抄系统" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="神庙·许愿" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="遭遇战·怪物PK" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="恶魔交易·特殊事件" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黄记小卖部" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社团会馆" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地点NPC对话" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地点信息" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发展目标·课后作业" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校外商店" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事件记录·截图存档" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学宫八卦小册" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="遭遇战·怪物PK" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="恶魔交易·特殊事件" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黄记小卖部" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="社团会馆" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地点NPC对话" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="地点信息" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="发展目标·课后作业" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="校外商店" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事件记录·截图存档" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -222,6 +223,421 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="1076325"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -613,7 +1029,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>学堂事件 / 考场(学科问答+突发事) / 自习室(小抄+和男主学习) / 神庙许愿 / 遭遇战PK(怪物) / 恶魔交易 / 命运线(男主剧情) / 社团会馆 / 商店 / 学宫八卦小册 / 兼职</t>
+          <t>学堂事件 / 考场(学科问答+突发事) / 自习室(小抄+和男主学习) / 神庙许愿 / 遭遇战PK(怪物) / 恶魔交易 / 学宫八卦小册(收集文本) / 命运线(男主剧情) / 社团会馆 / 商店 / 兼职</t>
         </is>
       </c>
     </row>
@@ -776,6 +1192,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>怪物/对手</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>立绘</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>事件内容</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>胜利奖励</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>失败惩罚</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>截图存档</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>雪怪</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>（怪物形象待截图）</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>（遭遇战事件内容）</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>胜利奖励统一奖励卡？</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>（失败惩罚）</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>对应上期'工作站 遭遇战v2.0'；巫之学宫/雪怪区域：前进不消耗通行骰子，怪物持续移动，需拉开距离。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -853,7 +1367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -867,7 +1381,7 @@
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,7 +1416,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="125" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>极品提神饮·灵药</t>
@@ -1063,10 +1577,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1251,20 +1766,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1294,48 +1809,52 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2" ht="125" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>黄记小卖部</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>黄大爷</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>小卖部没有零元购业务。</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>进入商店时</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr"/>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>视频168 约09分</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>考场</t>
+          <t>社团会馆</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>张鲁</t>
+          <t>（社团负责人）</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>（邻桌是张鲁，可借鉴试卷）</t>
+          <t>（固定台词待收集）</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>考试突发事</t>
+          <t>进入社团时</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr"/>
@@ -1343,116 +1862,47 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>校园约会</t>
+          <t>考场</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>法正</t>
+          <t>（监考/同场学生）</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>哦哦，魂魄……魂魄确实被我拿来用了啊。但他会昏迷，和我没关系。</t>
+          <t>（固定台词待收集）</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>剧情（周瑜昏迷真相）</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>视频170 约15分</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>颁奖典礼</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>学生会干部</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>万众瞩目的第一名——器部，虞翻！</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>剧情</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>视频169 约10分</t>
-        </is>
-      </c>
+          <t>考试时</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>颁奖典礼</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>袁基</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>感觉耳朵做得还是不像，眼睛……也能雕琢得再精巧些。</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>剧情</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr"/>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>⚠ 区分原则：本表只收【活动内容·地点固定台词】（NPC 口头禅/进店语等）；</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>学堂</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>（张角/张仲景/贾诩等老师）</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>（教师 NPC 台词）</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>学堂/剧情</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>对应上期'船夫 村集 博戏坊对话'；固定台词与剧情对白分开记录。</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>⚠ 剧情对白（如法正·周瑜昏迷真相、颁奖典礼、男主对话等）属于【主线剧情/命运线】，请录入「学宫史 主线+男主剧情线」「命运线·男主邂逅」，勿混入本表。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1750,7 +2200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1871,7 +2321,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1884,7 +2334,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1914,7 +2364,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="125" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>心纸裳·校服（傅融）</t>
@@ -1998,7 +2448,7 @@
       <c r="D5" s="10" t="inlineStr"/>
       <c r="E5" s="10" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="6" ht="125" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>心纸裳·校服（刘辩）</t>
@@ -2053,10 +2503,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2494,7 +2945,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2534,7 +2985,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="125" customHeight="1">
       <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
@@ -2569,7 +3020,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="125" customHeight="1">
       <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
@@ -2604,7 +3055,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="125" customHeight="1">
       <c r="A4" s="11" t="n">
         <v>3</v>
       </c>
@@ -2639,7 +3090,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="125" customHeight="1">
       <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
@@ -2688,14 +3139,11 @@
           <t>事件卡</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>（随机事件文本：学科+2 / +4 / +20(风水观) / 全学科+1）</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2706,6 +3154,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2726,7 +3175,7 @@
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2776,7 +3225,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="125" customHeight="1">
       <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
@@ -2821,7 +3270,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="125" customHeight="1">
       <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
@@ -2862,7 +3311,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="125" customHeight="1">
       <c r="A4" s="11" t="n">
         <v>3</v>
       </c>
@@ -2932,6 +3381,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2950,7 +3400,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2990,7 +3440,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="125" customHeight="1">
       <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
@@ -3034,6 +3484,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3051,7 +3502,7 @@
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3086,7 +3537,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="125" customHeight="1">
       <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
@@ -3187,6 +3638,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3294,16 +3746,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3314,74 +3764,104 @@
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>怪物/对手</t>
+          <t>条目名称</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>立绘</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>事件内容</t>
+          <t>收录状态</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>胜利奖励</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
-        <is>
-          <t>失败惩罚</t>
-        </is>
-      </c>
-      <c r="G1" s="8" t="inlineStr">
-        <is>
           <t>截图存档</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="10" t="n">
+    <row r="2" ht="125" customHeight="1">
+      <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>雪怪</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>（怪物形象待截图）</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>（遭遇战事件内容）</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>胜利奖励统一奖励卡？</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>（失败惩罚）</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr"/>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>学宫创世传说</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>相传灵灵七学宫创始者张良，昔年游历灵山，偶遇山中童子，授之以登仙修行之法。后人为纪念此事，遂于山中建宫立学，传道至今。</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>已收录</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>视频168 约34分</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="125" customHeight="1">
+      <c r="A3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>修行广场守则</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>禁止在修行广场摆摊、卖艺、乞讨、碰瓷、决斗、约会、打劫、尾随夫子、向夫子告白、不牵绳遛灵宠、不牵绳遛同学——</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>已收录</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>视频170 约22分</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>对应上期'工作站 遭遇战v2.0'；巫之学宫/雪怪区域：前进不消耗通行骰子，怪物持续移动，需拉开距离。</t>
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr"/>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>（八卦小册条目：每页一段文本+收录状态，从游戏内「学宫八卦」入口逐页翻阅记录）</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr"/>
+      <c r="E4" s="10" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>学宫八卦小册=本期可收集文本小册（活动内容），两条已按视频OCR收录，其余逐页补录；</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>注意：八卦小册与主线剧情不同，属玩法内收集文本。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>